--- a/Result/profitability/1788.xlsx
+++ b/Result/profitability/1788.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.92</v>
+        <v>1.975</v>
       </c>
       <c r="N2" t="n">
-        <v>25.83375</v>
+        <v>26.0375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.87625</v>
+        <v>1.96</v>
       </c>
       <c r="N3" t="n">
-        <v>24.835</v>
+        <v>25.3025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7975</v>
+        <v>1.84625</v>
       </c>
       <c r="N4" t="n">
-        <v>24.1375</v>
+        <v>24.46875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>1.59375</v>
+        <v>1.605</v>
       </c>
       <c r="N5" t="n">
-        <v>23.14</v>
+        <v>23.4275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1.41875</v>
+        <v>1.43875</v>
       </c>
       <c r="N6" t="n">
-        <v>21.79625</v>
+        <v>21.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.315</v>
+        <v>1.34625</v>
       </c>
       <c r="N7" t="n">
-        <v>20.61625</v>
+        <v>20.66</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1475</v>
+        <v>1.14125</v>
       </c>
       <c r="N8" t="n">
-        <v>19.14</v>
+        <v>19.1225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1108</v>
+      </c>
+      <c r="D75" t="n">
+        <v>793</v>
+      </c>
+      <c r="E75" t="n">
+        <v>314</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>119</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.75%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>126</v>
+      </c>
+      <c r="K75" t="n">
+        <v>102</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.04625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02136752136752129</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.004907115317209998</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04090909090909078</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08815638175546181</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
